--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137220422</v>
       </c>
       <c r="B2" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>137220498</v>
       </c>
       <c r="B3" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137220512</v>
       </c>
       <c r="B4" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>137220645</v>
       </c>
       <c r="B5" t="n">
-        <v>98241</v>
+        <v>98254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137220422</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>137220498</v>
       </c>
       <c r="B3" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>137220512</v>
       </c>
       <c r="B4" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>137220645</v>
       </c>
       <c r="B5" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -829,11 +829,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -939,11 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137220422</v>
       </c>
       <c r="B2" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137220645</v>
       </c>
       <c r="B5" t="n">
-        <v>98256</v>
+        <v>98259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137220422</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>137220498</v>
       </c>
       <c r="B3" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137220512</v>
       </c>
       <c r="B4" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137220645</v>
       </c>
       <c r="B5" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137220422</v>
       </c>
       <c r="B2" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137220645</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137220422</v>
       </c>
       <c r="B2" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>137220498</v>
       </c>
       <c r="B3" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137220512</v>
       </c>
       <c r="B4" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137220645</v>
       </c>
       <c r="B5" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137220422</v>
       </c>
       <c r="B2" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137220645</v>
       </c>
       <c r="B5" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137220422</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>137220498</v>
       </c>
       <c r="B3" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137220512</v>
       </c>
       <c r="B4" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137220645</v>
       </c>
       <c r="B5" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137220422</v>
       </c>
       <c r="B2" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137220645</v>
       </c>
       <c r="B5" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137220422</v>
       </c>
       <c r="B2" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137220645</v>
       </c>
       <c r="B5" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137220422</v>
       </c>
       <c r="B2" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137220645</v>
       </c>
       <c r="B5" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33206-2022 artfynd.xlsx
+++ b/artfynd/A 33206-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137220422</v>
       </c>
       <c r="B2" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>137220498</v>
       </c>
       <c r="B3" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137220512</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>137220645</v>
       </c>
       <c r="B5" t="n">
-        <v>98299</v>
+        <v>98303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
